--- a/artfynd/A 44438-2021 artfynd.xlsx
+++ b/artfynd/A 44438-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44438-2021 artfynd.xlsx
+++ b/artfynd/A 44438-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110914643</v>
+        <v>110914645</v>
       </c>
       <c r="B2" t="n">
-        <v>73681</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Näverbergsbäcken, Rättvik, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533924.9394681008</v>
+        <v>533881</v>
       </c>
       <c r="R2" t="n">
-        <v>6772438.582663344</v>
+        <v>6772381</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,30 +743,34 @@
           <t>2023-07-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-07-18</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -791,53 +787,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110914642</v>
+        <v>110914646</v>
       </c>
       <c r="B3" t="n">
-        <v>73681</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Näverbergsbäcken, Rättvik, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533913.6973631178</v>
+        <v>533869</v>
       </c>
       <c r="R3" t="n">
-        <v>6772448.634999702</v>
+        <v>6772381</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,30 +855,34 @@
           <t>2023-07-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-07-18</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -910,16 +902,11 @@
         <v>110914647</v>
       </c>
       <c r="B4" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -947,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533884.4387024323</v>
+        <v>533884</v>
       </c>
       <c r="R4" t="n">
-        <v>6772316.267343491</v>
+        <v>6772316</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,19 +967,9 @@
           <t>2023-07-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,15 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110914644</v>
+        <v>110914642</v>
       </c>
       <c r="B5" t="n">
-        <v>96265</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1050,34 +1022,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>6439</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Näverbergsbäcken, Rättvik, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>533893.2846523935</v>
+        <v>533914</v>
       </c>
       <c r="R5" t="n">
-        <v>6772404.410615748</v>
+        <v>6772448</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,27 +1082,18 @@
           <t>2023-07-18</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-07-18</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1143,6 +1109,204 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>110914643</v>
+      </c>
+      <c r="B6" t="n">
+        <v>83290</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Näverbergsbäcken, Rättvik, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>533925</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6772439</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>110914644</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Näverbergsbäcken, Rättvik, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>533893</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6772404</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44438-2021 artfynd.xlsx
+++ b/artfynd/A 44438-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110914645</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110914646</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110914647</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1109,6 +1129,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110914642</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1210,6 +1235,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110914643</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1307,8 +1337,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110914644</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>